--- a/tasks/HR_Troutly_T2_pto_liability_close/05_rubric_import.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/05_rubric_import.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -736,12 +736,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a total dollar liability of $92,739.54.</t>
+          <t>States, on the PTO liability page, a name and a department on every employee row.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>The cutover memo caps carryover at 40.0 hours, accrues four posted periods at the tier over 26 and values each balance at the rate on file over 2,080. The 52 rows sum to $92,739.54, or $92,772.88 rounding each posting.</t>
+          <t>The request lists employee ID, name, department, annual PTO tier, PTO balance, hourly rate and dollar liability as the table's columns, and the roster carries every name and department.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -751,25 +751,25 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K6" s="2" t="n"/>
@@ -791,40 +791,40 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, balances of 64.62, 64.62, 58.46, 58.46 and 58.46 hours for TRT-0005, TRT-0009, TRT-0014, TRT-0023 and TRT-0040, the five above 40.0 hours at 06/30/2026 whose balance the cap alone moves.</t>
+          <t>States, on the PTO liability page, the summary above one table of employee rows.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>The archive holds these five 06/30/2026 balances above 40.0 hours and the cutover memo caps carryover there. The HRIS report and the load file carry them uncapped, as the field mapping specified.</t>
+          <t>A short summary above one table is the shape the request sets, so the count and the totals come before the first employee row and no second employee table follows.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Final Response</t>
+          <t>Style / formatting</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/2026-06-24_Field_Mapping_Workbook.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}]</t>
         </is>
       </c>
       <c r="K7" s="2" t="n"/>
@@ -846,12 +846,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the 120-hour tier for TRT-0043, TRT-0051, TRT-0058, TRT-0079 and TRT-0083.</t>
+          <t>States, on the PTO liability page, a total dollar liability of $92,739.54.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>The archive and the offer letters date these five hires two to five years before 08/31/2026. The load file set HireDate to 07/01/2026 on them and BambooHR assigned the 80-hour policy from that date.</t>
+          <t>The cutover memo caps carryover at 40.0 hours, accrues four posted periods at the tier over 26 and values each balance at the rate on file over 2,080. The 52 rows sum to $92,739.54, or $92,772.88 rounding each posting.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K8" s="2" t="n"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the 160-hour tier for Samuel Burkenham, TRT-0071, with service bridged to 03/08/2021.</t>
+          <t>States, on the PTO liability page, a balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>The archive records Burkenham hired 03/08/2021, ended 08/25/2023 and rehired 04/22/2024, a 241-day break. The handbook's 7.6 bridges service across a break under 365 days, so his tier is 160 hours.</t>
+          <t>The archive holds Hosana's 06/30/2026 balance at 92.50 hours and the cutover memo caps carryover at 40.0 hours on that date. The HRIS report and the load file carry 92.50 uncapped, and four periods at the 160-hour tier add 24.62.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/2024-04-08_Rehire_Offer_TRT-0071.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Wiki/Onboarding_Data_Standards.md", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/2026-06-24_Field_Mapping_Workbook.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K9" s="2" t="n"/>
@@ -956,12 +956,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an accrual of 20.0000 hours for Marisela Thornbury, TRT-0018, three periods at the 120-hour tier and one at 160.</t>
+          <t>States, on the PTO liability page, the 120-hour tier for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>The archive dates Thornbury's service from 08/09/2021, so she reaches five years on 08/09/2026 inside the fourth posted period. The cutover memo moves the tier in that period, so three periods accrue 4.6154 hours and one 6.1538.</t>
+          <t>The archive and the offer letters date Kastellanos's hire 10/15/2021, four completed years before 08/31/2026. The load file set HireDate to 07/01/2026 and BambooHR assigned the 80-hour policy from that date.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K10" s="2" t="n"/>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $56.7308 for Yolanda Featherstone, TRT-0088.</t>
+          <t>States, on the PTO liability page, the 160-hour tier for Samuel Burkenham, TRT-0071.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>The signed promotion approval sets Featherstone's salary at $118,000.00 from 06/16/2026 and the handbook's 3.2 puts the signed document over the record. BambooHR carries $104,000.00. $118,000.00 over 2,080 is $56.7308.</t>
+          <t>The archive records Burkenham hired 03/08/2021, ended 08/25/2023 and rehired 04/22/2024, a 241-day break. The handbook's 7.6 bridges service across a break under 365 days, so his tier is 160 hours.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/2024-04-08_Rehire_Offer_TRT-0071.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Wiki/Onboarding_Data_Standards.md", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K11" s="2" t="n"/>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $71.2500 for Belaviv Luk, TRT-0117.</t>
+          <t>States, on the PTO liability page, a balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>The signed amendment sets Luk's salary at $148,200.00 from 05/16/2026 and the archive recorded it. BambooHR carries the loaded $138,000.00, and $148,200.00 over 2,080 is $71.2500.</t>
+          <t>The archive dates Thornbury's service from 08/09/2021 and her capped opening is 40.00 hours. She reaches five years on 08/09/2026 inside the fourth posted period, so the cutover memo accrues three periods of 4.6154 hours and one of 6.1538.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K12" s="2" t="n"/>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $29.3269 for Delphine Marchetti, TRT-0096.</t>
+          <t>States, on the PTO liability page, an hourly rate of $56.7308 for Yolanda Featherstone, TRT-0088.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Marchetti's offer letter carries the Support Specialist step on each anniversary and the handbook's 5.4 sets it at $3,000.00. Her anniversary fell 08/17/2026, so the rate on file is $61,000.00, $29.3269 an hour.</t>
+          <t>The signed promotion approval sets Featherstone's salary at $118,000.00 from 06/16/2026 and the handbook's 3.2 puts the signed document over the record. BambooHR carries $104,000.00. $118,000.00 over 2,080 is $56.7308.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Wiki/Compensation_Authority.md", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K13" s="2" t="n"/>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
+          <t>States, on the PTO liability page, an hourly rate of $71.2500 for Belaviv Luk, TRT-0117.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>The schedule change form moves Quintanilla from 25 to 32 hours a week on 08/10/2026 and the handbook's 2.2 accrues part-time hours pro-rata under 30. Three periods add 1.9231 hours and the fourth 3.0769 to 20.75.</t>
+          <t>The signed amendment sets Luk's salary at $148,200.00 from 05/16/2026 and the archive recorded it. BambooHR carries the loaded $138,000.00, and $148,200.00 over 2,080 is $71.2500.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K14" s="2" t="n"/>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
+          <t>States, on the PTO liability page, an hourly rate of $29.3269 for Delphine Marchetti, TRT-0096.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries CTR-2001 to CTR-2004 as active employees and the roster carries no contractor. The handbook bars contractors from paid time off.</t>
+          <t>Marchetti's offer letter carries the Support Specialist step on each anniversary and the handbook's 5.4 sets it at $3,000.00. Her anniversary fell 08/17/2026, so the rate on file is $61,000.00, $29.3269 an hour.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1246,25 +1246,25 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Wiki/Compensation_Authority.md", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K15" s="2" t="n"/>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for TRT-0037, TRT-0049, TRT-0064 or TRT-0006.</t>
+          <t>States, on the PTO liability page, a balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>The crosswalk marks TRT-0037, TRT-0049 and TRT-0064 Terminated, the archive ends each before 07/01/2026 and BambooHR ends TRT-0006 on 07/25/2026. The cutover memo excludes employment ended by 08/31/2026.</t>
+          <t>The schedule change form moves Quintanilla from 25 to 32 hours a week on 08/10/2026 and the handbook's 2.2 accrues part-time hours pro-rata under 30. Three periods add 1.9231 hours and the fourth 3.0769 to 20.75.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K16" s="2" t="n"/>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, Simone Okonkwo, TRT-0153, and Rafael Ibarra, TRT-0155, at the 80-hour tier with accruals since their start dates.</t>
+          <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Okonkwo started 07/22/2026 and Ibarra 08/03/2026 on the roster and the crosswalk marks both Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, so Okonkwo holds 6.15 hours and Ibarra 3.08.</t>
+          <t>BambooHR carries CTR-2001 to CTR-2004 as active employees and the roster carries no contractor. The handbook bars contractors from paid time off.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Offers/2026-07-02_Offer_TRT-0153_SIGNED.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K17" s="2" t="n"/>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002, four posted periods at the 160-hour tier.</t>
+          <t>States, on the PTO liability page, no row for Piper Athanasoulis, TRT-0037.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>The procedures memo posts four pay dates by 08/31/2026 and the fifth pays 09/04/2026. Jackson opens at 38.00 hours in the archive and adds 6.1538 in each of four periods at the 160-hour tier, 62.62 hours.</t>
+          <t>Athanasoulis ended 03/20/2026 on the archive and the crosswalk marks TRT-0037 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K18" s="2" t="n"/>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001, with 40.00 hours of approved time off deducted.</t>
+          <t>States, on the PTO liability page, no row for Halston Perevalov, TRT-0049.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>BambooHR holds Labeson's approved request of 40.00 hours from 07/06/2026 to 07/10/2026. The archive opens him at 38.25 hours and four periods at the 160-hour tier add 24.62, so he holds 22.87.</t>
+          <t>Perevalov ended 05/08/2026 on the archive and the crosswalk marks TRT-0049 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K19" s="2" t="n"/>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO policy the schedule's tier gives for each of the 6 employees whose loaded policy differed.</t>
+          <t>States, on the PTO liability page, no row for Marguerite Delacroix-Hahn, TRT-0064.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>The request asks that each PTO policy in BambooHR be the schedule's. Six migrated records carry the 80-hour policy from the loaded 07/01/2026 date, and the archive's dates put five at 120 hours and TRT-0071 at 160.</t>
+          <t>Delacroix-Hahn ended 06/15/2026 on the archive and the crosswalk marks TRT-0064 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1521,25 +1521,25 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K20" s="2" t="n"/>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance equal to the schedule's 08/31/2026 balance for every employee on the schedule.</t>
+          <t>States, on the PTO liability page, no row for Grayson Oshimoto, TRT-0006.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries the loaded balances, uncapped and at the loaded tiers. The request asks that each PTO balance in BambooHR be the schedule's, so all 52 balances read the schedule's 08/31/2026 figures.</t>
+          <t>Oshimoto ended 07/25/2026 in BambooHR and on the archive and the crosswalk marks TRT-0006 Terminated. The cutover memo excludes employment ended by 08/31/2026.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1576,25 +1576,25 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K21" s="2" t="n"/>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance row for TRT-0153 and TRT-0155.</t>
+          <t>States, on the PTO liability page, a balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Neither Okonkwo nor Ibarra has a BambooHR row and the crosswalk marks both Never Loaded. The request asks for the PTO balance in BambooHR for every employee on the schedule, so each has a balance row.</t>
+          <t>Okonkwo started 07/22/2026 on the roster and the crosswalk marks TRT-0153 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours in each of the two periods since the start.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
@@ -1644,17 +1644,402 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Offers/2026-07-02_Offer_TRT-0153_SIGNED.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>States, on the PTO liability page, a balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Ibarra started 08/03/2026 on the roster and the crosswalk marks TRT-0155 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours in the one period since the start.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Expert Assessment</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>The procedures memo posts four pay dates by 08/31/2026 and the fifth pays 09/04/2026. Jackson opens at 38.00 hours in the archive and adds 6.1538 in each of four periods at the 160-hour tier, 62.62 hours.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>BambooHR holds Labeson's approved request of 40.00 hours from 07/06/2026 to 07/10/2026. The archive opens him at 38.25 hours and four periods at the 160-hour tier add 24.62, so he holds 22.87.</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO policy matching the schedule's tier for each of the 50 employees on the schedule other than TRT-0153 and TRT-0155.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Each PTO policy in BambooHR is asked by the request to be the schedule's. Six loaded records carry the 80-hour policy from the loaded 07/01/2026 date, and the archive's dates put five at 120 hours and TRT-0071 at 160.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Expert Assessment</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance equal to the schedule's 08/31/2026 balance for each of the 50 employees on the schedule other than TRT-0153 and TRT-0155.</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>BambooHR carries the loaded balances, uncapped and at the loaded tiers. The request asks that each PTO balance in BambooHR be the schedule's, so all 50 loaded balances read the schedule's 08/31/2026 figures.</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Expert Assessment</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>No BambooHR row exists for Okonkwo and the crosswalk marks TRT-0153 Never Loaded. The request asks for the PTO balance in BambooHR for every employee on the schedule, so a row carrying 6.15 hours is created.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Ibarra has no BambooHR row and the crosswalk marks TRT-0155 Never Loaded. The request asks for the PTO balance in BambooHR for every employee on the schedule, so a row carrying 3.08 hours is created.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/tasks/HR_Troutly_T2_pto_liability_close/05_rubric_import.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/05_rubric_import.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -626,12 +626,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, hours to two decimals, hourly rates to four decimals, dollars to the cent and a total equal to the sum of the rows.</t>
+          <t>States, on the PTO liability page, hours to two decimals, hourly rates to four decimals and dollars to the cent.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The request sets hours to two decimals, rates to four, dollars to the cent and the total as the sum of the rows, as the handbook's 7.3 totals them.</t>
+          <t>The request sets hours to two decimals, rates to four and dollars to the cent, the precision the July close carried.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}]</t>
         </is>
       </c>
       <c r="K4" s="2" t="n"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a summary with the employee count, the total hours and the total dollar liability.</t>
+          <t>States, on the PTO liability page, a total dollar liability equal to the sum of the rows.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>The summary the request asks for states the employee count, the total hours and the total dollar liability.</t>
+          <t>The request makes the total the sum of the rows and the handbook's 7.3 totals the rounded rows the same way.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K5" s="2" t="n"/>
@@ -736,12 +736,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a name and a department on every employee row.</t>
+          <t>States, on the PTO liability page, a summary with the employee count, the total hours and the total dollar liability.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>The request lists employee ID, name, department, annual PTO tier, PTO balance, hourly rate and dollar liability as the table's columns, and the roster carries every name and department.</t>
+          <t>The summary the request asks for states the employee count, the total hours and the total dollar liability.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}]</t>
         </is>
       </c>
       <c r="K6" s="2" t="n"/>
@@ -791,17 +791,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the summary above one table of employee rows.</t>
+          <t>States, on the PTO liability page, a name, a department and an annual PTO tier on every employee row.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>A short summary above one table is the shape the request sets, so the count and the totals come before the first employee row and no second employee table follows.</t>
+          <t>The request lists employee ID, name, department, annual PTO tier, PTO balance, hourly rate and dollar liability as the table's columns, and the roster carries every name and department.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Style / formatting</t>
+          <t>Final Response</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K7" s="2" t="n"/>
@@ -846,40 +846,40 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a total dollar liability of $92,739.54.</t>
+          <t>States, on the PTO liability page, an employee ID on every row.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>The cutover memo caps carryover at 40.0 hours, accrues four posted periods at the tier over 26 and values each balance at the rate on file over 2,080. The 52 rows sum to $92,739.54, or $92,772.88 rounding each posting.</t>
+          <t>An employee ID on every row is the request's own form line, and the roster keys every current employee on one.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Final Response</t>
+          <t>Style / formatting</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K8" s="2" t="n"/>
@@ -901,40 +901,40 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
+          <t>States, on the PTO liability page, every date in MM/DD/YYYY form.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>The archive holds Hosana's 06/30/2026 balance at 92.50 hours and the cutover memo caps carryover at 40.0 hours on that date. The HRIS report and the load file carry 92.50 uncapped, and four periods at the 160-hour tier add 24.62.</t>
+          <t>Dates MM/DD/YYYY is the request's form line, and every Troutly record from the roster to the procedures memo writes them that way.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Final Response</t>
+          <t>Style / formatting</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/2026-06-24_Field_Mapping_Workbook.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K9" s="2" t="n"/>
@@ -956,40 +956,40 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the 120-hour tier for Oren Kastellanos, TRT-0043.</t>
+          <t>States, on the PTO liability page, the summary above one table of employee rows.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>The archive and the offer letters date Kastellanos's hire 10/15/2021, four completed years before 08/31/2026. The load file set HireDate to 07/01/2026 and BambooHR assigned the 80-hour policy from that date.</t>
+          <t>A short summary above one table is the shape the request sets, so the count and the totals come before the first employee row and no second employee table follows.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Final Response</t>
+          <t>Style / formatting</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}]</t>
         </is>
       </c>
       <c r="K10" s="2" t="n"/>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the 160-hour tier for Samuel Burkenham, TRT-0071.</t>
+          <t>States, on the PTO liability page, a total dollar liability of $92,739.54.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>The archive records Burkenham hired 03/08/2021, ended 08/25/2023 and rehired 04/22/2024, a 241-day break. The handbook's 7.6 bridges service across a break under 365 days, so his tier is 160 hours.</t>
+          <t>The cutover memo caps carryover at 40.0 hours, accrues four posted periods at the tier over 26 and values each balance at the rate on file over 2,080. The 52 rows sum to $92,739.54, or $92,772.88 rounding each posting.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/2024-04-08_Rehire_Offer_TRT-0071.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Wiki/Onboarding_Data_Standards.md", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K11" s="2" t="n"/>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
+          <t>States, on the PTO liability page, a balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>The archive dates Thornbury's service from 08/09/2021 and her capped opening is 40.00 hours. She reaches five years on 08/09/2026 inside the fourth posted period, so the cutover memo accrues three periods of 4.6154 hours and one of 6.1538.</t>
+          <t>The archive holds Hosana's 06/30/2026 balance at 92.50 hours and the cutover memo caps carryover at 40.0 hours on that date. The HRIS report and the load file carry 92.50 uncapped, and four periods at the 160-hour tier add 24.62.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/2026-06-24_Field_Mapping_Workbook.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K12" s="2" t="n"/>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $56.7308 for Yolanda Featherstone, TRT-0088.</t>
+          <t>States, on the PTO liability page, the 120-hour tier for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>The signed promotion approval sets Featherstone's salary at $118,000.00 from 06/16/2026 and the handbook's 3.2 puts the signed document over the record. BambooHR carries $104,000.00. $118,000.00 over 2,080 is $56.7308.</t>
+          <t>The archive and the offer letters date Kastellanos's hire 10/15/2021, four completed years before 08/31/2026. The load file set HireDate to 07/01/2026 and BambooHR assigned the 80-hour policy from that date.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K13" s="2" t="n"/>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $71.2500 for Belaviv Luk, TRT-0117.</t>
+          <t>States, on the PTO liability page, the 160-hour tier for Samuel Burkenham, TRT-0071.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>The signed amendment sets Luk's salary at $148,200.00 from 05/16/2026 and the archive recorded it. BambooHR carries the loaded $138,000.00, and $148,200.00 over 2,080 is $71.2500.</t>
+          <t>The archive records Burkenham hired 03/08/2021, ended 08/25/2023 and rehired 04/22/2024, a 241-day break. The handbook's 7.6 bridges service across a break under 365 days, so his tier is 160 hours.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/2024-04-08_Rehire_Offer_TRT-0071.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Wiki/Onboarding_Data_Standards.md", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K14" s="2" t="n"/>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $29.3269 for Delphine Marchetti, TRT-0096.</t>
+          <t>States, on the PTO liability page, a balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Marchetti's offer letter carries the Support Specialist step on each anniversary and the handbook's 5.4 sets it at $3,000.00. Her anniversary fell 08/17/2026, so the rate on file is $61,000.00, $29.3269 an hour.</t>
+          <t>The archive dates Thornbury's service from 08/09/2021 and her capped opening is 40.00 hours. She reaches five years on 08/09/2026 inside the fourth posted period, so the cutover memo accrues three periods of 4.6154 hours and one of 6.1538.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Wiki/Compensation_Authority.md", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K15" s="2" t="n"/>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
+          <t>States, on the PTO liability page, an hourly rate of $56.7308 for Yolanda Featherstone, TRT-0088.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>The schedule change form moves Quintanilla from 25 to 32 hours a week on 08/10/2026 and the handbook's 2.2 accrues part-time hours pro-rata under 30. Three periods add 1.9231 hours and the fourth 3.0769 to 20.75.</t>
+          <t>The signed promotion approval sets Featherstone's salary at $118,000.00 from 06/16/2026 and the handbook's 3.2 puts the signed document over the record. BambooHR carries $104,000.00. $118,000.00 over 2,080 is $56.7308.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K16" s="2" t="n"/>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
+          <t>States, on the PTO liability page, an hourly rate of $71.2500 for Belaviv Luk, TRT-0117.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries CTR-2001 to CTR-2004 as active employees and the roster carries no contractor. The handbook bars contractors from paid time off.</t>
+          <t>The signed amendment sets Luk's salary at $148,200.00 from 05/16/2026 and the archive recorded it. BambooHR carries the loaded $138,000.00, and $148,200.00 over 2,080 is $71.2500.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1356,25 +1356,25 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K17" s="2" t="n"/>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Piper Athanasoulis, TRT-0037.</t>
+          <t>States, on the PTO liability page, an hourly rate of $29.3269 for Delphine Marchetti, TRT-0096.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Athanasoulis ended 03/20/2026 on the archive and the crosswalk marks TRT-0037 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
+          <t>Marchetti's offer letter carries the Support Specialist step on each anniversary and the handbook's 5.4 sets it at $3,000.00. Her anniversary fell 08/17/2026, so the rate on file is $61,000.00, $29.3269 an hour.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1411,25 +1411,25 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Wiki/Compensation_Authority.md", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K18" s="2" t="n"/>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Halston Perevalov, TRT-0049.</t>
+          <t>States, on the PTO liability page, a balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Perevalov ended 05/08/2026 on the archive and the crosswalk marks TRT-0049 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
+          <t>The schedule change form moves Quintanilla from 25 to 32 hours a week on 08/10/2026 and the handbook's 2.2 accrues part-time hours pro-rata under 30. Three periods add 1.9231 hours and the fourth 3.0769 to 20.75.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1466,25 +1466,25 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K19" s="2" t="n"/>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Marguerite Delacroix-Hahn, TRT-0064.</t>
+          <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Delacroix-Hahn ended 06/15/2026 on the archive and the crosswalk marks TRT-0064 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
+          <t>BambooHR carries CTR-2001 to CTR-2004 as active employees and the roster carries no contractor. The handbook bars contractors from paid time off.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K20" s="2" t="n"/>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Grayson Oshimoto, TRT-0006.</t>
+          <t>States, on the PTO liability page, no row for Piper Athanasoulis, TRT-0037.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Oshimoto ended 07/25/2026 in BambooHR and on the archive and the crosswalk marks TRT-0006 Terminated. The cutover memo excludes employment ended by 08/31/2026.</t>
+          <t>Athanasoulis ended 03/20/2026 on the archive and the crosswalk marks TRT-0037 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+          <t>States, on the PTO liability page, no row for Halston Perevalov, TRT-0049.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Okonkwo started 07/22/2026 on the roster and the crosswalk marks TRT-0153 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours in each of the two periods since the start.</t>
+          <t>Perevalov ended 05/08/2026 on the archive and the crosswalk marks TRT-0049 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1631,25 +1631,25 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Offers/2026-07-02_Offer_TRT-0153_SIGNED.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K22" s="2" t="n"/>
@@ -1671,12 +1671,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+          <t>States, on the PTO liability page, no row for Marguerite Delacroix-Hahn, TRT-0064.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Ibarra started 08/03/2026 on the roster and the crosswalk marks TRT-0155 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours in the one period since the start.</t>
+          <t>Delacroix-Hahn ended 06/15/2026 on the archive and the crosswalk marks TRT-0064 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1686,25 +1686,25 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K23" s="2" t="n"/>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002.</t>
+          <t>States, on the PTO liability page, no row for Grayson Oshimoto, TRT-0006.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>The procedures memo posts four pay dates by 08/31/2026 and the fifth pays 09/04/2026. Jackson opens at 38.00 hours in the archive and adds 6.1538 in each of four periods at the 160-hour tier, 62.62 hours.</t>
+          <t>Oshimoto ended 07/25/2026 in BambooHR and on the archive and the crosswalk marks TRT-0006 Terminated. The cutover memo excludes employment ended by 08/31/2026.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K24" s="2" t="n"/>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001.</t>
+          <t>States, on the PTO liability page, a balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>BambooHR holds Labeson's approved request of 40.00 hours from 07/06/2026 to 07/10/2026. The archive opens him at 38.25 hours and four periods at the 160-hour tier add 24.62, so he holds 22.87.</t>
+          <t>Okonkwo started 07/22/2026 on the roster and the crosswalk marks TRT-0153 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours in each of the two periods since the start.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Offers/2026-07-02_Offer_TRT-0153_SIGNED.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K25" s="2" t="n"/>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO policy matching the schedule's tier for each of the 50 employees on the schedule other than TRT-0153 and TRT-0155.</t>
+          <t>States, on the PTO liability page, a balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Each PTO policy in BambooHR is asked by the request to be the schedule's. Six loaded records carry the 80-hour policy from the loaded 07/01/2026 date, and the archive's dates put five at 120 hours and TRT-0071 at 160.</t>
+          <t>Ibarra started 08/03/2026 on the roster and the crosswalk marks TRT-0155 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours in the one period since the start.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K26" s="2" t="n"/>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance equal to the schedule's 08/31/2026 balance for each of the 50 employees on the schedule other than TRT-0153 and TRT-0155.</t>
+          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries the loaded balances, uncapped and at the loaded tiers. The request asks that each PTO balance in BambooHR be the schedule's, so all 50 loaded balances read the schedule's 08/31/2026 figures.</t>
+          <t>The procedures memo posts four pay dates by 08/31/2026 and the fifth pays 09/04/2026. Jackson opens at 38.00 hours in the archive and adds 6.1538 in each of four periods at the 160-hour tier, 62.62 hours.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1906,25 +1906,25 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K27" s="2" t="n"/>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>No BambooHR row exists for Okonkwo and the crosswalk marks TRT-0153 Never Loaded. The request asks for the PTO balance in BambooHR for every employee on the schedule, so a row carrying 6.15 hours is created.</t>
+          <t>BambooHR holds Labeson's approved request of 40.00 hours from 07/06/2026 to 07/10/2026. The archive opens him at 38.25 hours and four periods at the 160-hour tier add 24.62, so he holds 22.87.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K28" s="2" t="n"/>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Ibarra has no BambooHR row and the crosswalk marks TRT-0155 Never Loaded. The request asks for the PTO balance in BambooHR for every employee on the schedule, so a row carrying 3.08 hours is created.</t>
+          <t>Kastellanos carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 10/15/2021, four completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
@@ -2029,17 +2029,842 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Priyamvada Raghunath, TRT-0051.</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Raghunath carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 05/03/2022, four completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Expert Assessment</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Callum Oyelaran, TRT-0058.</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Oyelaran carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 09/12/2022, three completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Expert Assessment</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO 5 Plus Years policy for Samuel Burkenham, TRT-0071.</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Burkenham carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates service from 03/08/2021, bridged over a 241-day break by the handbook's 7.6, so the schedule's tier is 160 hours.</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Expert Assessment</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Wren Takahashi-Bell, TRT-0079.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Takahashi-Bell carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 02/06/2023, three completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Expert Assessment</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Desmond Achterberg, TRT-0083.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Achterberg carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 06/19/2023, three completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Expert Assessment</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, no PTO policy change on the 44 employees whose loaded policy is the schedule's tier.</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>The load file put 44 of the 50 loaded records on the policy the archive's dates give, and the request asks that BambooHR carry the schedule's policy, which leaves those 44 as loaded.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>BambooHR carries Hosana's loaded balance of 117.12 hours. The schedule's 64.62 follows the cutover memo's 40.0-hour cap at 06/30/2026, and the request asks that the balance in BambooHR be the schedule's.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Expert Assessment</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 34.46 hours for Oren Kastellanos, TRT-0043.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>BambooHR carries Kastellanos's loaded balance of 31.81 hours. The schedule's 34.46 follows the 120-hour tier the archive's 10/15/2021 hire date gives, and the request asks that the balance in BambooHR be the schedule's.</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Expert Assessment</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 51.87 hours for Samuel Burkenham, TRT-0071.</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>BambooHR carries Burkenham's loaded balance of 39.56 hours. The schedule's 51.87 follows the 160-hour tier the handbook's 7.6 gives the bridged service, and the request asks that the balance in BambooHR be the schedule's.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Expert Assessment</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>BambooHR carries Thornbury's loaded balance of 87.87 hours. The schedule's 60.00 follows the tier change inside the fourth posted period under the cutover memo, and the request asks that the balance in BambooHR be the schedule's.</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Expert Assessment</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>BambooHR carries Quintanilla's loaded balance of 33.06 hours. The schedule's 29.60 follows the schedule change form's part-time hours under the handbook's 2.2, and the request asks that the balance in BambooHR be the schedule's.</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Expert Assessment</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, no PTO balance change on the 33 employees whose loaded balance is the schedule's.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>The loaded balances agree with the schedule on 33 of the 50 BambooHR records, where no rule the cutover memo or the handbook adds moves the figure, and the request asks that BambooHR carry the schedule's balance.</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>No BambooHR row exists for Okonkwo and the crosswalk marks TRT-0153 Never Loaded. The request asks for the PTO balance in BambooHR for every employee on the schedule, so a row carrying 6.15 hours is created.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Ibarra has no BambooHR row and the crosswalk marks TRT-0155 Never Loaded. The request asks for the PTO balance in BambooHR for every employee on the schedule, so a row carrying 3.08 hours is created.</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>States, in Greenhouse, every table as seeded, with no row added, changed or removed.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Change nothing in Greenhouse is the request's own line, and the two hires' candidate rows there are read and never written.</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/tasks/HR_Troutly_T2_pto_liability_close/05_rubric_import.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/05_rubric_import.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, no PTO policy change on the 44 employees whose loaded policy is the schedule's tier.</t>
+          <t>States, in BambooHR, the schedule's PTO policy for each of the 44 employees whose loaded policy is the schedule's tier.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, no PTO balance change on the 33 employees whose loaded balance is the schedule's.</t>
+          <t>States, in BambooHR, the schedule's PTO balance for each of the 33 employees whose loaded balance is the schedule's.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>States, in Greenhouse, every table as seeded, with no row added, changed or removed.</t>
+          <t>States, in BambooHR, the PTO Under 2 Years policy for Simone Okonkwo, TRT-0153.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Change nothing in Greenhouse is the request's own line, and the two hires' candidate rows there are read and never written.</t>
+          <t>Okonkwo's created row carries the 80-hour policy, the schedule's tier for a 07/22/2026 start with under two years of service. The request asks for the schedule's PTO policy in BambooHR for every employee on the schedule.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2859,12 +2859,67 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO Under 2 Years policy for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Ibarra's created row carries the 80-hour policy, the schedule's tier for a 08/03/2026 start with under two years of service. The request asks for the schedule's PTO policy in BambooHR for every employee on the schedule.</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/tasks/HR_Troutly_T2_pto_liability_close/05_rubric_import.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/05_rubric_import.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -571,12 +571,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the 52 current employees at 08/31/2026 as the only employee rows.</t>
+          <t>States, on the PTO liability page, an employee row for each of the 52 current employees at 08/31/2026.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The request defines a current employee as anyone employed by Troutly on 08/31/2026. The roster carries 52. BambooHR's 57 active rows hold four contractors and three ended employees and lack two hires.</t>
+          <t>The request defines a current employee as anyone employed by Troutly on 08/31/2026 and the roster carries 52. BambooHR's active rows lack the two hires who started after cutover.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, hours to two decimals, hourly rates to four decimals and dollars to the cent.</t>
+          <t>States, on the PTO liability page, hours to two decimals.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The request sets hours to two decimals, rates to four and dollars to the cent, the precision the July close carried.</t>
+          <t>Hours to two decimals is the request's form line, and the July close carried its balance column at that precision.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -681,17 +681,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a total dollar liability equal to the sum of the rows.</t>
+          <t>States, on the PTO liability page, hourly rates to four decimals.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>The request makes the total the sum of the rows and the handbook's 7.3 totals the rounded rows the same way.</t>
+          <t>Hourly rates to four decimals is the request's form line, and the July close's rate formula rounds to four.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Final Response</t>
+          <t>Style / formatting</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}]</t>
         </is>
       </c>
       <c r="K5" s="2" t="n"/>
@@ -736,17 +736,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a summary with the employee count, the total hours and the total dollar liability.</t>
+          <t>States, on the PTO liability page, dollars to the cent.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>The summary the request asks for states the employee count, the total hours and the total dollar liability.</t>
+          <t>Dollars to the cent is the request's form line, and the July close carried its liability column at that precision.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Final Response</t>
+          <t>Style / formatting</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a name, a department and an annual PTO tier on every employee row.</t>
+          <t>States, on the PTO liability page, a total dollar liability equal to the sum of the rows.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>The request lists employee ID, name, department, annual PTO tier, PTO balance, hourly rate and dollar liability as the table's columns, and the roster carries every name and department.</t>
+          <t>The request makes the total the sum of the rows and the handbook's 7.3 totals the rounded rows the same way.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K7" s="2" t="n"/>
@@ -846,17 +846,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an employee ID on every row.</t>
+          <t>States, on the PTO liability page, a summary with the employee count, the total hours and the total dollar liability.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>An employee ID on every row is the request's own form line, and the roster keys every current employee on one.</t>
+          <t>The summary the request asks for states the employee count, the total hours and the total dollar liability.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Style / formatting</t>
+          <t>Final Response</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}]</t>
         </is>
       </c>
       <c r="K8" s="2" t="n"/>
@@ -901,17 +901,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, every date in MM/DD/YYYY form.</t>
+          <t>States, on the PTO liability page, a name on every employee row.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Dates MM/DD/YYYY is the request's form line, and every Troutly record from the roster to the procedures memo writes them that way.</t>
+          <t>A name on every employee row is the request's column list, and the roster carries every current employee's name.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Style / formatting</t>
+          <t>Final Response</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K9" s="2" t="n"/>
@@ -956,17 +956,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the summary above one table of employee rows.</t>
+          <t>States, on the PTO liability page, a department on every employee row.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>A short summary above one table is the shape the request sets, so the count and the totals come before the first employee row and no second employee table follows.</t>
+          <t>Every employee row carries a department in the request's column list, and the roster and the org chart carry each employee's department.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Style / formatting</t>
+          <t>Final Response</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K10" s="2" t="n"/>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a total dollar liability of $92,739.54.</t>
+          <t>States, on the PTO liability page, an annual PTO tier in hours on every employee row.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>The cutover memo caps carryover at 40.0 hours, accrues four posted periods at the tier over 26 and values each balance at the rate on file over 2,080. The 52 rows sum to $92,739.54, or $92,772.88 rounding each posting.</t>
+          <t>The annual PTO tier in hours is the request's fourth column, and the cutover memo's table names the three values it can take.</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1026,25 +1026,25 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K11" s="2" t="n"/>
@@ -1066,40 +1066,40 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
+          <t>States, on the PTO liability page, an employee ID on every row.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>The archive holds Hosana's 06/30/2026 balance at 92.50 hours and the cutover memo caps carryover at 40.0 hours on that date. The HRIS report and the load file carry 92.50 uncapped, and four periods at the 160-hour tier add 24.62.</t>
+          <t>An employee ID on every row is the request's own form line, and the roster keys every current employee on one.</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Final Response</t>
+          <t>Style / formatting</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/2026-06-24_Field_Mapping_Workbook.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K12" s="2" t="n"/>
@@ -1121,40 +1121,40 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the 120-hour tier for Oren Kastellanos, TRT-0043.</t>
+          <t>States, on the PTO liability page, every date in MM/DD/YYYY form.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>The archive and the offer letters date Kastellanos's hire 10/15/2021, four completed years before 08/31/2026. The load file set HireDate to 07/01/2026 and BambooHR assigned the 80-hour policy from that date.</t>
+          <t>Dates MM/DD/YYYY is the request's form line, and every Troutly record from the roster to the procedures memo writes them that way.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Final Response</t>
+          <t>Style / formatting</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K13" s="2" t="n"/>
@@ -1176,40 +1176,40 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, the 160-hour tier for Samuel Burkenham, TRT-0071.</t>
+          <t>States, on the PTO liability page, the summary above one table of employee rows.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>The archive records Burkenham hired 03/08/2021, ended 08/25/2023 and rehired 04/22/2024, a 241-day break. The handbook's 7.6 bridges service across a break under 365 days, so his tier is 160 hours.</t>
+          <t>A short summary above one table is the shape the request sets, so the count and the totals come before the first employee row and no second employee table follows.</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Final Response</t>
+          <t>Style / formatting</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/2024-04-08_Rehire_Offer_TRT-0071.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Wiki/Onboarding_Data_Standards.md", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}]</t>
         </is>
       </c>
       <c r="K14" s="2" t="n"/>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
+          <t>States, on the PTO liability page, a total dollar liability of $92,739.54.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>The archive dates Thornbury's service from 08/09/2021 and her capped opening is 40.00 hours. She reaches five years on 08/09/2026 inside the fourth posted period, so the cutover memo accrues three periods of 4.6154 hours and one of 6.1538.</t>
+          <t>The cutover memo caps carryover at 40.0 hours, accrues four posted periods at the tier over 26 and values each balance at the rate on file over 2,080. The 52 rows sum to $92,739.54, or $92,772.88 rounding each posting.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K15" s="2" t="n"/>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $56.7308 for Yolanda Featherstone, TRT-0088.</t>
+          <t>States, on the PTO liability page, a balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>The signed promotion approval sets Featherstone's salary at $118,000.00 from 06/16/2026 and the handbook's 3.2 puts the signed document over the record. BambooHR carries $104,000.00. $118,000.00 over 2,080 is $56.7308.</t>
+          <t>The archive holds Hosana's 06/30/2026 balance at 92.50 hours and the cutover memo caps carryover at 40.0 hours on that date. The HRIS report and the load file carry 92.50 uncapped, and four periods at the 160-hour tier add 24.62.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/HRIS_Time_Off_Report_2026-08-31.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/2026-06-24_Field_Mapping_Workbook.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K16" s="2" t="n"/>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $71.2500 for Belaviv Luk, TRT-0117.</t>
+          <t>States, on the PTO liability page, the 120-hour tier for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>The signed amendment sets Luk's salary at $148,200.00 from 05/16/2026 and the archive recorded it. BambooHR carries the loaded $138,000.00, and $148,200.00 over 2,080 is $71.2500.</t>
+          <t>The archive and the offer letters date Kastellanos's hire 10/15/2021, four completed years before 08/31/2026. The load file set HireDate to 07/01/2026 and BambooHR assigned the 80-hour policy from that date.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K17" s="2" t="n"/>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an hourly rate of $29.3269 for Delphine Marchetti, TRT-0096.</t>
+          <t>States, on the PTO liability page, the 160-hour tier for Samuel Burkenham, TRT-0071.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Marchetti's offer letter carries the Support Specialist step on each anniversary and the handbook's 5.4 sets it at $3,000.00. Her anniversary fell 08/17/2026, so the rate on file is $61,000.00, $29.3269 an hour.</t>
+          <t>The archive records Burkenham hired 03/08/2021, ended 08/25/2023 and rehired 04/22/2024, a 241-day break. The handbook's 7.6 bridges service across a break under 365 days, so his tier is 160 hours.</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Wiki/Compensation_Authority.md", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/2024-04-08_Rehire_Offer_TRT-0071.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Wiki/Onboarding_Data_Standards.md", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K18" s="2" t="n"/>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
+          <t>States, on the PTO liability page, a balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>The schedule change form moves Quintanilla from 25 to 32 hours a week on 08/10/2026 and the handbook's 2.2 accrues part-time hours pro-rata under 30. Three periods add 1.9231 hours and the fourth 3.0769 to 20.75.</t>
+          <t>The archive dates Thornbury's service from 08/09/2021 and her capped opening is 40.00 hours. She reaches five years on 08/09/2026 inside the fourth posted period, so the cutover memo accrues three periods of 4.6154 hours and one of 6.1538.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K19" s="2" t="n"/>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
+          <t>States, on the PTO liability page, an hourly rate of $56.7308 for Yolanda Featherstone, TRT-0088.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries CTR-2001 to CTR-2004 as active employees and the roster carries no contractor. The handbook bars contractors from paid time off.</t>
+          <t>The signed promotion approval sets Featherstone's salary at $118,000.00 from 06/16/2026 and the handbook's 3.2 puts the signed document over the record. BambooHR carries $104,000.00. $118,000.00 over 2,080 is $56.7308.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1521,25 +1521,25 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Comp/Promotions/2026-06-10_Promotion_Approval_TRT-0088.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K20" s="2" t="n"/>
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Piper Athanasoulis, TRT-0037.</t>
+          <t>States, on the PTO liability page, an hourly rate of $71.2500 for Belaviv Luk, TRT-0117.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Athanasoulis ended 03/20/2026 on the archive and the crosswalk marks TRT-0037 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
+          <t>The signed amendment sets Luk's salary at $148,200.00 from 05/16/2026 and the archive recorded it. BambooHR carries the loaded $138,000.00, and $148,200.00 over 2,080 is $71.2500.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1576,25 +1576,25 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Comp/Amendments/2026-05-12_Comp_Amendment_TRT-0117.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K21" s="2" t="n"/>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Halston Perevalov, TRT-0049.</t>
+          <t>States, on the PTO liability page, an hourly rate of $29.3269 for Delphine Marchetti, TRT-0096.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Perevalov ended 05/08/2026 on the archive and the crosswalk marks TRT-0049 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
+          <t>Marchetti's offer letter carries the Support Specialist step on each anniversary and the handbook's 5.4 sets it at $3,000.00. Her anniversary fell 08/17/2026, so the rate on file is $61,000.00, $29.3269 an hour.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1631,25 +1631,25 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Wiki/Compensation_Authority.md", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K22" s="2" t="n"/>
@@ -1671,12 +1671,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Marguerite Delacroix-Hahn, TRT-0064.</t>
+          <t>States, on the PTO liability page, a balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Delacroix-Hahn ended 06/15/2026 on the archive and the crosswalk marks TRT-0064 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
+          <t>The schedule change form moves Quintanilla from 25 to 32 hours a week on 08/10/2026 and the handbook's 2.2 accrues part-time hours pro-rata under 30. Three periods add 1.9231 hours and the fourth 3.0769 to 20.75.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1686,25 +1686,25 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Benefits/2026-08-10_Schedule_Change_TRT-0141.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K23" s="2" t="n"/>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Grayson Oshimoto, TRT-0006.</t>
+          <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Oshimoto ended 07/25/2026 in BambooHR and on the archive and the crosswalk marks TRT-0006 Terminated. The cutover memo excludes employment ended by 08/31/2026.</t>
+          <t>BambooHR carries CTR-2001 to CTR-2004 as active employees and the roster carries no contractor. The handbook bars contractors from paid time off.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K24" s="2" t="n"/>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+          <t>States, on the PTO liability page, no row for Piper Athanasoulis, TRT-0037.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Okonkwo started 07/22/2026 on the roster and the crosswalk marks TRT-0153 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours in each of the two periods since the start.</t>
+          <t>Athanasoulis ended 03/20/2026 on the archive and the crosswalk marks TRT-0037 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1796,25 +1796,25 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Offers/2026-07-02_Offer_TRT-0153_SIGNED.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K25" s="2" t="n"/>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+          <t>States, on the PTO liability page, no row for Halston Perevalov, TRT-0049.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Ibarra started 08/03/2026 on the roster and the crosswalk marks TRT-0155 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours in the one period since the start.</t>
+          <t>Perevalov ended 05/08/2026 on the archive and the crosswalk marks TRT-0049 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K26" s="2" t="n"/>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002.</t>
+          <t>States, on the PTO liability page, no row for Marguerite Delacroix-Hahn, TRT-0064.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>The procedures memo posts four pay dates by 08/31/2026 and the fifth pays 09/04/2026. Jackson opens at 38.00 hours in the archive and adds 6.1538 in each of four periods at the 160-hour tier, 62.62 hours.</t>
+          <t>Delacroix-Hahn ended 06/15/2026 on the archive and the crosswalk marks TRT-0064 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K27" s="2" t="n"/>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001.</t>
+          <t>States, on the PTO liability page, no row for Grayson Oshimoto, TRT-0006.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>BambooHR holds Labeson's approved request of 40.00 hours from 07/06/2026 to 07/10/2026. The archive opens him at 38.25 hours and four periods at the 160-hour tier add 24.62, so he holds 22.87.</t>
+          <t>Oshimoto ended 07/25/2026 in BambooHR and on the archive and the crosswalk marks TRT-0006 Terminated. The cutover memo excludes employment ended by 08/31/2026.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K28" s="2" t="n"/>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Oren Kastellanos, TRT-0043.</t>
+          <t>States, on the PTO liability page, a balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Kastellanos carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 10/15/2021, four completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
+          <t>Okonkwo started 07/22/2026 on the roster and the crosswalk marks TRT-0153 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours in each of the two periods since the start.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Offers/2026-07-02_Offer_TRT-0153_SIGNED.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K29" s="2" t="n"/>
@@ -2056,12 +2056,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Priyamvada Raghunath, TRT-0051.</t>
+          <t>States, on the PTO liability page, a balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Raghunath carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 05/03/2022, four completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
+          <t>Ibarra started 08/03/2026 on the roster and the crosswalk marks TRT-0155 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours in the one period since the start.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K30" s="2" t="n"/>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Callum Oyelaran, TRT-0058.</t>
+          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Oyelaran carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 09/12/2022, three completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
+          <t>The procedures memo posts four pay dates by 08/31/2026 and the fifth pays 09/04/2026. Jackson opens at 38.00 hours in the archive and adds 6.1538 in each of four periods at the 160-hour tier, 62.62 hours.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2126,25 +2126,25 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K31" s="2" t="n"/>
@@ -2166,12 +2166,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 5 Plus Years policy for Samuel Burkenham, TRT-0071.</t>
+          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Burkenham carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates service from 03/08/2021, bridged over a 241-day break by the handbook's 7.6, so the schedule's tier is 160 hours.</t>
+          <t>BambooHR holds Labeson's approved request of 40.00 hours from 07/06/2026 to 07/10/2026. The archive opens him at 38.25 hours and four periods at the 160-hour tier add 24.62, so he holds 22.87.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2181,25 +2181,25 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K32" s="2" t="n"/>
@@ -2221,12 +2221,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Wren Takahashi-Bell, TRT-0079.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Takahashi-Bell carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 02/06/2023, three completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
+          <t>Kastellanos carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 10/15/2021, four completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Desmond Achterberg, TRT-0083.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Priyamvada Raghunath, TRT-0051.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Achterberg carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 06/19/2023, three completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
+          <t>Raghunath carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 05/03/2022, four completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the schedule's PTO policy for each of the 44 employees whose loaded policy is the schedule's tier.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Callum Oyelaran, TRT-0058.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>The load file put 44 of the 50 loaded records on the policy the archive's dates give, and the request asks that BambooHR carry the schedule's policy, which leaves those 44 as loaded.</t>
+          <t>Oyelaran carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 09/12/2022, three completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
+          <t>States, in BambooHR, the PTO 5 Plus Years policy for Samuel Burkenham, TRT-0071.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries Hosana's loaded balance of 117.12 hours. The schedule's 64.62 follows the cutover memo's 40.0-hour cap at 06/30/2026, and the request asks that the balance in BambooHR be the schedule's.</t>
+          <t>Burkenham carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates service from 03/08/2021, bridged over a 241-day break by the handbook's 7.6, so the schedule's tier is 160 hours.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K36" s="2" t="n"/>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 34.46 hours for Oren Kastellanos, TRT-0043.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Wren Takahashi-Bell, TRT-0079.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries Kastellanos's loaded balance of 31.81 hours. The schedule's 34.46 follows the 120-hour tier the archive's 10/15/2021 hire date gives, and the request asks that the balance in BambooHR be the schedule's.</t>
+          <t>Takahashi-Bell carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 02/06/2023, three completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K37" s="2" t="n"/>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 51.87 hours for Samuel Burkenham, TRT-0071.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Desmond Achterberg, TRT-0083.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries Burkenham's loaded balance of 39.56 hours. The schedule's 51.87 follows the 160-hour tier the handbook's 7.6 gives the bridged service, and the request asks that the balance in BambooHR be the schedule's.</t>
+          <t>Achterberg carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 06/19/2023, three completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K38" s="2" t="n"/>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
+          <t>States, in BambooHR, for the 44 employees whose loaded policy is the tier's at 08/31/2026, the PTO Under 2 Years policy for TRT-0096, TRT-0099, TRT-0102, TRT-0105, TRT-0108, TRT-0110, TRT-0113, TRT-0119, TRT-0122, TRT-0128, TRT-0131, TRT-0135, TRT-0141, TRT-0150, TRT-0154, TRT-0156, the PTO 2 to 5 Years policy for TRT-0012, TRT-0014, TRT-0021, TRT-0023, TRT-0027, TRT-0029, TRT-0031, TRT-0034, TRT-0040, TRT-0045, TRT-0047, TRT-0052, TRT-0055, TRT-0062, TRT-0066, TRT-0069, TRT-0074, TRT-0076, TRT-0086, TRT-0088, TRT-0091, TRT-0093, TRT-0117, the PTO 5 Plus Years policy for TRT-0001, TRT-0002, TRT-0005, TRT-0009, TRT-0018.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries Thornbury's loaded balance of 87.87 hours. The schedule's 60.00 follows the tier change inside the fourth posted period under the cutover memo, and the request asks that the balance in BambooHR be the schedule's.</t>
+          <t>The load file put 44 of the 50 loaded records on the policy the archive's dates give, and the request asks that BambooHR carry the schedule's policy, which leaves those 44 as loaded.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K39" s="2" t="n"/>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
+          <t>States, in BambooHR, a PTO balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries Quintanilla's loaded balance of 33.06 hours. The schedule's 29.60 follows the schedule change form's part-time hours under the handbook's 2.2, and the request asks that the balance in BambooHR be the schedule's.</t>
+          <t>BambooHR carries Hosana's loaded balance of 117.12 hours. The schedule's 64.62 follows the cutover memo's 40.0-hour cap at 06/30/2026, and the request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the schedule's PTO balance for each of the 33 employees whose loaded balance is the schedule's.</t>
+          <t>States, in BambooHR, a PTO balance of 34.46 hours for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>The loaded balances agree with the schedule on 33 of the 50 BambooHR records, where no rule the cutover memo or the handbook adds moves the figure, and the request asks that BambooHR carry the schedule's balance.</t>
+          <t>BambooHR carries Kastellanos's loaded balance of 31.81 hours. The schedule's 34.46 follows the 120-hour tier the archive's 10/15/2021 hire date gives, and the request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+          <t>States, in BambooHR, a PTO balance of 51.87 hours for Samuel Burkenham, TRT-0071.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>No BambooHR row exists for Okonkwo and the crosswalk marks TRT-0153 Never Loaded. The request asks for the PTO balance in BambooHR for every employee on the schedule, so a row carrying 6.15 hours is created.</t>
+          <t>BambooHR carries Burkenham's loaded balance of 39.56 hours. The schedule's 51.87 follows the 160-hour tier the handbook's 7.6 gives the bridged service, and the request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K42" s="2" t="n"/>
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+          <t>States, in BambooHR, a PTO balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Ibarra has no BambooHR row and the crosswalk marks TRT-0155 Never Loaded. The request asks for the PTO balance in BambooHR for every employee on the schedule, so a row carrying 3.08 hours is created.</t>
+          <t>BambooHR carries Thornbury's loaded balance of 87.87 hours. The schedule's 60.00 follows the tier change inside the fourth posted period under the cutover memo, and the request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K43" s="2" t="n"/>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO Under 2 Years policy for Simone Okonkwo, TRT-0153.</t>
+          <t>States, in BambooHR, a PTO balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Okonkwo's created row carries the 80-hour policy, the schedule's tier for a 07/22/2026 start with under two years of service. The request asks for the schedule's PTO policy in BambooHR for every employee on the schedule.</t>
+          <t>BambooHR carries Quintanilla's loaded balance of 33.06 hours. The schedule's 29.60 follows the schedule change form's part-time hours under the handbook's 2.2, and the request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
@@ -2854,12 +2854,12 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K44" s="2" t="n"/>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO Under 2 Years policy for Rafael Ibarra, TRT-0155.</t>
+          <t>States, in BambooHR, for the 33 employees whose loaded balance is the 08/31/2026 figure, a PTO balance of 22.87 hours for TRT-0001, 62.62 for TRT-0002, 26.71 for TRT-0027, 30.96 for TRT-0034, 7.96 for TRT-0045, 5.46 for TRT-0047, 4.46 for TRT-0052, 15.96 for TRT-0055, 21.21 for TRT-0062, 27.96 for TRT-0066, 46.21 for TRT-0069, 44.21 for TRT-0074, 35.21 for TRT-0076, 51.96 for TRT-0086, 13.21 for TRT-0088, 25.71 for TRT-0091, 20.21 for TRT-0093, 20.56 for TRT-0096, 37.06 for TRT-0099, 24.31 for TRT-0102, 15.81 for TRT-0105, 41.31 for TRT-0108, 23.81 for TRT-0110, 26.56 for TRT-0113, 8.46 for TRT-0117, 22.06 for TRT-0119, 31.31 for TRT-0122, 20.06 for TRT-0128, 4.31 for TRT-0131, 49.31 for TRT-0135, 12.31 for TRT-0150, 3.08 for TRT-0154, 0.00 for TRT-0156.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Ibarra's created row carries the 80-hour policy, the schedule's tier for a 08/03/2026 start with under two years of service. The request asks for the schedule's PTO policy in BambooHR for every employee on the schedule.</t>
+          <t>The loaded balances agree with the schedule on 33 of the 50 BambooHR records, where no rule the cutover memo or the handbook adds moves the figure, and the request asks that BambooHR carry the schedule's balance.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2914,12 +2914,232 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>No BambooHR row exists for Okonkwo and the crosswalk marks TRT-0153 Never Loaded. The request asks for the PTO balance in BambooHR for every employee on the schedule, so a row carrying 6.15 hours is created.</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Ibarra has no BambooHR row and the crosswalk marks TRT-0155 Never Loaded. The request asks for the PTO balance in BambooHR for every employee on the schedule, so a row carrying 3.08 hours is created.</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO Under 2 Years policy for Simone Okonkwo, TRT-0153.</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Okonkwo's created row carries the 80-hour policy, the schedule's tier for a 07/22/2026 start with under two years of service. The request asks for the schedule's PTO policy in BambooHR for every employee on the schedule.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO Under 2 Years policy for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Ibarra's created row carries the 80-hour policy, the schedule's tier for a 08/03/2026 start with under two years of service. The request asks for the schedule's PTO policy in BambooHR for every employee on the schedule.</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>

--- a/tasks/HR_Troutly_T2_pto_liability_close/05_rubric_import.xlsx
+++ b/tasks/HR_Troutly_T2_pto_liability_close/05_rubric_import.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -571,12 +571,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, an employee row for each of the 52 current employees at 08/31/2026.</t>
+          <t>States, on the PTO liability page, the 52 current employees at 08/31/2026 as the only employee rows.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The request defines a current employee as anyone employed by Troutly on 08/31/2026 and the roster carries 52. BambooHR's active rows lack the two hires who started after cutover.</t>
+          <t>The request defines a current employee as anyone employed by Troutly on 08/31/2026. The roster carries 52. BambooHR's 57 active rows hold four contractors and three ended employees and lack two hires.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no contractor row, CTR-2001 to CTR-2004.</t>
+          <t>States, on the PTO liability page, a balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries CTR-2001 to CTR-2004 as active employees and the roster carries no contractor. The handbook bars contractors from paid time off.</t>
+          <t>Okonkwo started 07/22/2026 on the roster and the crosswalk marks TRT-0153 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours in each of the two periods since the start.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1741,25 +1741,25 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/Employee_Handbook_v3.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Offers/2026-07-02_Offer_TRT-0153_SIGNED.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K24" s="2" t="n"/>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Piper Athanasoulis, TRT-0037.</t>
+          <t>States, on the PTO liability page, a balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Athanasoulis ended 03/20/2026 on the archive and the crosswalk marks TRT-0037 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
+          <t>Ibarra started 08/03/2026 on the roster and the crosswalk marks TRT-0155 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours in the one period since the start.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1796,25 +1796,25 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K25" s="2" t="n"/>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Halston Perevalov, TRT-0049.</t>
+          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Perevalov ended 05/08/2026 on the archive and the crosswalk marks TRT-0049 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
+          <t>The procedures memo posts four pay dates by 08/31/2026 and the fifth pays 09/04/2026. Jackson opens at 38.00 hours in the archive and adds 6.1538 in each of four periods at the 160-hour tier, 62.62 hours.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K26" s="2" t="n"/>
@@ -1891,12 +1891,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Marguerite Delacroix-Hahn, TRT-0064.</t>
+          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Delacroix-Hahn ended 06/15/2026 on the archive and the crosswalk marks TRT-0064 Terminated, while BambooHR still reads Active. The cutover memo excludes employment ended by 08/31/2026.</t>
+          <t>BambooHR holds Labeson's approved request of 40.00 hours from 07/06/2026 to 07/10/2026. The archive opens him at 38.25 hours and four periods at the 160-hour tier add 24.62, so he holds 22.87.</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K27" s="2" t="n"/>
@@ -1946,12 +1946,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, no row for Grayson Oshimoto, TRT-0006.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Oshimoto ended 07/25/2026 in BambooHR and on the archive and the crosswalk marks TRT-0006 Terminated. The cutover memo excludes employment ended by 08/31/2026.</t>
+          <t>Kastellanos carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 10/15/2021, four completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K28" s="2" t="n"/>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Priyamvada Raghunath, TRT-0051.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Okonkwo started 07/22/2026 on the roster and the crosswalk marks TRT-0153 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours in each of the two periods since the start.</t>
+          <t>Raghunath carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 05/03/2022, four completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/Recruiting/Offers/2026-07-02_Offer_TRT-0153_SIGNED.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K29" s="2" t="n"/>
@@ -2056,12 +2056,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Callum Oyelaran, TRT-0058.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Ibarra started 08/03/2026 on the roster and the crosswalk marks TRT-0155 Never Loaded. The cutover memo accrues each posted period at the 80-hour tier, 3.0769 hours in the one period since the start.</t>
+          <t>Oyelaran carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 09/12/2022, three completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/People/Offer_Letters/Historical_Offer_Letters_2020-2026.pdf", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K30" s="2" t="n"/>
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 62.62 hours for Sora Jackson, TRT-0002.</t>
+          <t>States, in BambooHR, the PTO 5 Plus Years policy for Samuel Burkenham, TRT-0071.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>The procedures memo posts four pay dates by 08/31/2026 and the fifth pays 09/04/2026. Jackson opens at 38.00 hours in the archive and adds 6.1538 in each of four periods at the 160-hour tier, 62.62 hours.</t>
+          <t>Burkenham carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates service from 03/08/2021, bridged over a 241-day break by the handbook's 7.6, so the schedule's tier is 160 hours.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2126,25 +2126,25 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Payroll/2026-06-25_Payroll_Procedures_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K31" s="2" t="n"/>
@@ -2166,12 +2166,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>States, on the PTO liability page, a balance of 22.87 hours for Michael Labeson, TRT-0001.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Wren Takahashi-Bell, TRT-0079.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>BambooHR holds Labeson's approved request of 40.00 hours from 07/06/2026 to 07/10/2026. The archive opens him at 38.25 hours and four periods at the 160-hour tier add 24.62, so he holds 22.87.</t>
+          <t>Takahashi-Bell carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 02/06/2023, three completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2181,25 +2181,25 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K32" s="2" t="n"/>
@@ -2221,12 +2221,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Oren Kastellanos, TRT-0043.</t>
+          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Desmond Achterberg, TRT-0083.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Kastellanos carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 10/15/2021, four completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
+          <t>Achterberg carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 06/19/2023, three completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Priyamvada Raghunath, TRT-0051.</t>
+          <t>States, in BambooHR, for the 44 employees whose loaded policy is the tier's at 08/31/2026, the PTO Under 2 Years policy for TRT-0096, TRT-0099, TRT-0102, TRT-0105, TRT-0108, TRT-0110, TRT-0113, TRT-0119, TRT-0122, TRT-0128, TRT-0131, TRT-0135, TRT-0141, TRT-0150, TRT-0154, TRT-0156, the PTO 2 to 5 Years policy for TRT-0012, TRT-0014, TRT-0021, TRT-0023, TRT-0027, TRT-0029, TRT-0031, TRT-0034, TRT-0040, TRT-0045, TRT-0047, TRT-0052, TRT-0055, TRT-0062, TRT-0066, TRT-0069, TRT-0074, TRT-0076, TRT-0086, TRT-0088, TRT-0091, TRT-0093, TRT-0117, the PTO 5 Plus Years policy for TRT-0001, TRT-0002, TRT-0005, TRT-0009, TRT-0018.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Raghunath carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 05/03/2022, four completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
+          <t>The load file put 44 of the 50 loaded records on the policy the archive's dates give, and the request asks that BambooHR carry the schedule's policy, which leaves those 44 as loaded.</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Expert Assessment</t>
+          <t>Objective Compliance</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Callum Oyelaran, TRT-0058.</t>
+          <t>States, in BambooHR, a PTO balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Oyelaran carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 09/12/2022, three completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
+          <t>BambooHR carries Hosana's loaded balance of 117.12 hours. The schedule's 64.62 follows the cutover memo's 40.0-hour cap at 06/30/2026, and the request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K35" s="2" t="n"/>
@@ -2386,12 +2386,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 5 Plus Years policy for Samuel Burkenham, TRT-0071.</t>
+          <t>States, in BambooHR, a PTO balance of 34.46 hours for Oren Kastellanos, TRT-0043.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Burkenham carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates service from 03/08/2021, bridged over a 241-day break by the handbook's 7.6, so the schedule's tier is 160 hours.</t>
+          <t>BambooHR carries Kastellanos's loaded balance of 31.81 hours. The schedule's 34.46 follows the 120-hour tier the archive's 10/15/2021 hire date gives, and the request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K36" s="2" t="n"/>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Wren Takahashi-Bell, TRT-0079.</t>
+          <t>States, in BambooHR, a PTO balance of 51.87 hours for Samuel Burkenham, TRT-0071.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Takahashi-Bell carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 02/06/2023, three completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
+          <t>BambooHR carries Burkenham's loaded balance of 39.56 hours. The schedule's 51.87 follows the 160-hour tier the handbook's 7.6 gives the bridged service, and the request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K37" s="2" t="n"/>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO 2 to 5 Years policy for Desmond Achterberg, TRT-0083.</t>
+          <t>States, in BambooHR, a PTO balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Achterberg carries the PTO Under 2 Years policy in BambooHR, loaded 07/01/2026. The archive dates the hire 06/19/2023, three completed years before 08/31/2026, so the schedule's tier is 120 hours.</t>
+          <t>BambooHR carries Thornbury's loaded balance of 87.87 hours. The schedule's 60.00 follows the tier change inside the fourth posted period under the cutover memo, and the request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K38" s="2" t="n"/>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, for the 44 employees whose loaded policy is the tier's at 08/31/2026, the PTO Under 2 Years policy for TRT-0096, TRT-0099, TRT-0102, TRT-0105, TRT-0108, TRT-0110, TRT-0113, TRT-0119, TRT-0122, TRT-0128, TRT-0131, TRT-0135, TRT-0141, TRT-0150, TRT-0154, TRT-0156, the PTO 2 to 5 Years policy for TRT-0012, TRT-0014, TRT-0021, TRT-0023, TRT-0027, TRT-0029, TRT-0031, TRT-0034, TRT-0040, TRT-0045, TRT-0047, TRT-0052, TRT-0055, TRT-0062, TRT-0066, TRT-0069, TRT-0074, TRT-0076, TRT-0086, TRT-0088, TRT-0091, TRT-0093, TRT-0117, the PTO 5 Plus Years policy for TRT-0001, TRT-0002, TRT-0005, TRT-0009, TRT-0018.</t>
+          <t>States, in BambooHR, a PTO balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>The load file put 44 of the 50 loaded records on the policy the archive's dates give, and the request asks that BambooHR carry the schedule's policy, which leaves those 44 as loaded.</t>
+          <t>BambooHR carries Quintanilla's loaded balance of 33.06 hours. The schedule's 29.60 follows the schedule change form's part-time hours under the handbook's 2.2, and the request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/HRIS_Import_Load_2026-07-01.csv", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K39" s="2" t="n"/>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 64.62 hours for Mikelle Hosana, TRT-0005.</t>
+          <t>States, in BambooHR, a PTO balance of 64.62 hours for Krystale Jumawan, TRT-0009.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries Hosana's loaded balance of 117.12 hours. The schedule's 64.62 follows the cutover memo's 40.0-hour cap at 06/30/2026, and the request asks that the balance in BambooHR be the schedule's.</t>
+          <t>Jumawan carries a loaded balance of 108.62 hours in BambooHR, and the schedule's 64.62 follows the cutover memo's 40.0-hour cap at 06/30/2026. The request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 34.46 hours for Oren Kastellanos, TRT-0043.</t>
+          <t>States, in BambooHR, a PTO balance of 18.46 hours for Jessica Ko, TRT-0012.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries Kastellanos's loaded balance of 31.81 hours. The schedule's 34.46 follows the 120-hour tier the archive's 10/15/2021 hire date gives, and the request asks that the balance in BambooHR be the schedule's.</t>
+          <t>Ko carries a loaded balance of 49.96 hours in BambooHR, and the schedule's 18.46 follows the cutover memo's 40.0-hour cap at 06/30/2026. The request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 51.87 hours for Samuel Burkenham, TRT-0071.</t>
+          <t>States, in BambooHR, a PTO balance of 58.46 hours for Rohan Iyer, TRT-0014.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries Burkenham's loaded balance of 39.56 hours. The schedule's 51.87 follows the 160-hour tier the handbook's 7.6 gives the bridged service, and the request asks that the balance in BambooHR be the schedule's.</t>
+          <t>Iyer carries a loaded balance of 84.46 hours in BambooHR, and the schedule's 58.46 follows the cutover memo's 40.0-hour cap at 06/30/2026. The request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 60.00 hours for Marisela Thornbury, TRT-0018.</t>
+          <t>States, in BambooHR, a PTO balance of 42.46 hours for Edith Bustamante, TRT-0021.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries Thornbury's loaded balance of 87.87 hours. The schedule's 60.00 follows the tier change inside the fourth posted period under the cutover memo, and the request asks that the balance in BambooHR be the schedule's.</t>
+          <t>Bustamante carries a loaded balance of 76.46 hours in BambooHR, and the schedule's 42.46 follows the cutover memo's 40.0-hour cap at 06/30/2026. The request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 29.60 hours for Beatriz Quintanilla, TRT-0141.</t>
+          <t>States, in BambooHR, a PTO balance of 58.46 hours for Maeve Oyinlola, TRT-0023.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>BambooHR carries Quintanilla's loaded balance of 33.06 hours. The schedule's 29.60 follows the schedule change form's part-time hours under the handbook's 2.2, and the request asks that the balance in BambooHR be the schedule's.</t>
+          <t>Oyinlola carries a loaded balance of 78.96 hours in BambooHR, and the schedule's 58.46 follows the cutover memo's 40.0-hour cap at 06/30/2026. The request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, for the 33 employees whose loaded balance is the 08/31/2026 figure, a PTO balance of 22.87 hours for TRT-0001, 62.62 for TRT-0002, 26.71 for TRT-0027, 30.96 for TRT-0034, 7.96 for TRT-0045, 5.46 for TRT-0047, 4.46 for TRT-0052, 15.96 for TRT-0055, 21.21 for TRT-0062, 27.96 for TRT-0066, 46.21 for TRT-0069, 44.21 for TRT-0074, 35.21 for TRT-0076, 51.96 for TRT-0086, 13.21 for TRT-0088, 25.71 for TRT-0091, 20.21 for TRT-0093, 20.56 for TRT-0096, 37.06 for TRT-0099, 24.31 for TRT-0102, 15.81 for TRT-0105, 41.31 for TRT-0108, 23.81 for TRT-0110, 26.56 for TRT-0113, 8.46 for TRT-0117, 22.06 for TRT-0119, 31.31 for TRT-0122, 20.06 for TRT-0128, 4.31 for TRT-0131, 49.31 for TRT-0135, 12.31 for TRT-0150, 3.08 for TRT-0154, 0.00 for TRT-0156.</t>
+          <t>States, in BambooHR, a PTO balance of 50.46 hours for Emeka Thorsen, TRT-0029.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>The loaded balances agree with the schedule on 33 of the 50 BambooHR records, where no rule the cutover memo or the handbook adds moves the figure, and the request asks that BambooHR carry the schedule's balance.</t>
+          <t>Thorsen carries a loaded balance of 67.46 hours in BambooHR, and the schedule's 50.46 follows the cutover memo's 40.0-hour cap at 06/30/2026. The request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+          <t>States, in BambooHR, a PTO balance of 26.46 hours for Zephyr Adebayo, TRT-0031.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>No BambooHR row exists for Okonkwo and the crosswalk marks TRT-0153 Never Loaded. The request asks for the PTO balance in BambooHR for every employee on the schedule, so a row carrying 6.15 hours is created.</t>
+          <t>Adebayo carries a loaded balance of 38.46 hours in BambooHR, and the schedule's 26.46 follows the cutover memo's 40.0-hour cap at 06/30/2026. The request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K46" s="2" t="n"/>
@@ -2991,12 +2991,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, a PTO balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+          <t>States, in BambooHR, a PTO balance of 58.46 hours for Ilse Van der Kolk, TRT-0040.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Ibarra has no BambooHR row and the crosswalk marks TRT-0155 Never Loaded. The request asks for the PTO balance in BambooHR for every employee on the schedule, so a row carrying 3.08 hours is created.</t>
+          <t>Kolk carries a loaded balance of 67.96 hours in BambooHR, and the schedule's 58.46 follows the cutover memo's 40.0-hour cap at 06/30/2026. The request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K47" s="2" t="n"/>
@@ -3046,12 +3046,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO Under 2 Years policy for Simone Okonkwo, TRT-0153.</t>
+          <t>States, in BambooHR, a PTO balance of 6.71 hours for Priyamvada Raghunath, TRT-0051.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Okonkwo's created row carries the 80-hour policy, the schedule's tier for a 07/22/2026 start with under two years of service. The request asks for the schedule's PTO policy in BambooHR for every employee on the schedule.</t>
+          <t>Raghunath carries a loaded balance of 0.56 hours in BambooHR, and the schedule's 6.71 follows the 120-hour tier the archive's 05/03/2022 hire date gives. The request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K48" s="2" t="n"/>
@@ -3101,12 +3101,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>States, in BambooHR, the PTO Under 2 Years policy for Rafael Ibarra, TRT-0155.</t>
+          <t>States, in BambooHR, a PTO balance of 40.96 hours for Callum Oyelaran, TRT-0058.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Ibarra's created row carries the 80-hour policy, the schedule's tier for a 08/03/2026 start with under two years of service. The request asks for the schedule's PTO policy in BambooHR for every employee on the schedule.</t>
+          <t>Oyelaran carries a loaded balance of 34.81 hours in BambooHR, and the schedule's 40.96 follows the 120-hour tier the archive's 09/12/2022 hire date gives. The request asks that the balance in BambooHR be the schedule's.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Objective Compliance</t>
+          <t>Expert Assessment</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
@@ -3129,17 +3129,402 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
         </is>
       </c>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 24.96 hours for Wren Takahashi-Bell, TRT-0079.</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Takahashi-Bell carries a loaded balance of 18.81 hours in BambooHR, and the schedule's 24.96 follows the 120-hour tier the archive's 02/06/2023 hire date gives. The request asks that the balance in BambooHR be the schedule's.</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Expert Assessment</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 18.71 hours for Desmond Achterberg, TRT-0083.</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Achterberg carries a loaded balance of 12.56 hours in BambooHR, and the schedule's 18.71 follows the 120-hour tier the archive's 06/19/2023 hire date gives. The request asks that the balance in BambooHR be the schedule's.</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Expert Assessment</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, for the 33 employees whose loaded balance is the 08/31/2026 figure, a PTO balance of 22.87 hours for TRT-0001, 62.62 for TRT-0002, 26.71 for TRT-0027, 30.96 for TRT-0034, 7.96 for TRT-0045, 5.46 for TRT-0047, 4.46 for TRT-0052, 15.96 for TRT-0055, 21.21 for TRT-0062, 27.96 for TRT-0066, 46.21 for TRT-0069, 44.21 for TRT-0074, 35.21 for TRT-0076, 51.96 for TRT-0086, 13.21 for TRT-0088, 25.71 for TRT-0091, 20.21 for TRT-0093, 20.56 for TRT-0096, 37.06 for TRT-0099, 24.31 for TRT-0102, 15.81 for TRT-0105, 41.31 for TRT-0108, 23.81 for TRT-0110, 26.56 for TRT-0113, 8.46 for TRT-0117, 22.06 for TRT-0119, 31.31 for TRT-0122, 20.06 for TRT-0128, 4.31 for TRT-0131, 49.31 for TRT-0135, 12.31 for TRT-0150, 3.08 for TRT-0154, 0.00 for TRT-0156.</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>The loaded balances agree with the schedule on 33 of the 50 BambooHR records, where no rule the cutover memo or the handbook adds moves the figure, and the request asks that BambooHR carry the schedule's balance.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Policies/2026-06-20_PTO_Policy_Cutover_Memo.docx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/Migration/SplinterHR_Final_Archive_2026-07-28.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 6.15 hours for Simone Okonkwo, TRT-0153.</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>No BambooHR row exists for Okonkwo and the crosswalk marks TRT-0153 Never Loaded. The request asks for the PTO balance in BambooHR for every employee on the schedule, so a row carrying 6.15 hours is created.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, a PTO balance of 3.08 hours for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Ibarra has no BambooHR row and the crosswalk marks TRT-0155 Never Loaded. The request asks for the PTO balance in BambooHR for every employee on the schedule, so a row carrying 3.08 hours is created.</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO Under 2 Years policy for Simone Okonkwo, TRT-0153.</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Okonkwo's created row carries the 80-hour policy, the schedule's tier for a 07/22/2026 start with under two years of service. The request asks for the schedule's PTO policy in BambooHR for every employee on the schedule.</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>App DB Programatic</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>States, in BambooHR, the PTO Under 2 Years policy for Rafael Ibarra, TRT-0155.</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Ibarra's created row carries the 80-hour policy, the schedule's tier for a 08/03/2026 start with under two years of service. The request asks for the schedule's PTO policy in BambooHR for every employee on the schedule.</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Final Response</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Objective Compliance</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>[{"name": "filesystem/pto_liability_request.pdf", "index": null, "source": "task", "snapshotId": "snap_45e68b376f2547dca61408b65d8ba774", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-31_Master_Employee_Roster.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}, {"name": "filesystem/HR/Data/2026-08-28_Employee_ID_Crosswalk.xlsx", "index": null, "source": "world", "snapshotId": "snap_c6f6a0879f3d47a19048ee80d7529157", "transformations": []}]</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
